--- a/output/pdf_financials_xlsx/MI.UN.xlsx
+++ b/output/pdf_financials_xlsx/MI.UN.xlsx
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.928</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.878</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.166</v>
       </c>
     </row>
     <row r="35">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.928</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.878</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.166</v>
       </c>
     </row>
     <row r="37">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">

--- a/output/pdf_financials_xlsx/MI.UN.xlsx
+++ b/output/pdf_financials_xlsx/MI.UN.xlsx
@@ -2240,21 +2240,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>3.422</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.539</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>13.072</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>16.205</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>22.636</v>
       </c>
     </row>
     <row r="68">
@@ -2269,10 +2267,8 @@
       <c r="C68" s="3" t="n">
         <v>20.018</v>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D68" s="3" t="n">
+        <v>13.072</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>42.109</v>
